--- a/12625637.xlsx
+++ b/12625637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B08642C-1A5A-43F7-BE91-34428D9EC733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64302803-BA4B-46B2-B080-E0DCCDDF86F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>HEADACHE</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -1344,27 +1347,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="15">
+      <c r="A13" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B13" s="14">
+        <v>200</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>250</v>
+      </c>
+      <c r="E13" s="14">
+        <v>10</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13"/>

--- a/12625637.xlsx
+++ b/12625637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64302803-BA4B-46B2-B080-E0DCCDDF86F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95E4EFA4-B3E4-4C32-9122-0826CD430260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1393,73 +1399,145 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="15">
+      <c r="A14" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B14" s="14">
+        <v>257.142857142857</v>
+      </c>
+      <c r="C14" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>33</v>
+      </c>
+      <c r="F14" s="14">
+        <v>416.66666666666703</v>
+      </c>
+      <c r="G14" s="14">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>50</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>959.30952380952408</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>480.69047619047592</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15">
+      <c r="A15" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B15" s="14">
+        <v>241.42857142857099</v>
+      </c>
+      <c r="C15" s="14">
+        <v>25</v>
+      </c>
+      <c r="D15" s="14">
+        <v>130</v>
+      </c>
+      <c r="E15" s="14">
+        <v>68</v>
+      </c>
+      <c r="F15" s="14">
+        <v>541.66666666666697</v>
+      </c>
+      <c r="G15" s="14">
+        <v>10</v>
+      </c>
+      <c r="H15" s="14">
+        <v>10</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1016.095238095238</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>423.90476190476204</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15">
+      <c r="A16" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B16" s="14">
+        <v>225.71428571428601</v>
+      </c>
+      <c r="C16" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="D16" s="14">
+        <v>80</v>
+      </c>
+      <c r="E16" s="14">
+        <v>103</v>
+      </c>
+      <c r="F16" s="14">
+        <v>666.66666666666697</v>
+      </c>
+      <c r="G16" s="14">
+        <v>12</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1132.880952380953</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14">
+        <v>307.11904761904702</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
